--- a/InputData/land/AOCoLUPpUA/Annual Ongoing Cost of Land Use Pol per Unit Area.xlsx
+++ b/InputData/land/AOCoLUPpUA/Annual Ongoing Cost of Land Use Pol per Unit Area.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olivia\Documents\EPS_Models by Region\RMI\All_states_RMI\LA\land\AOCoLUPpUA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nathaniyer/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/LA/land/AOCoLUPpUA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A3AD433-0667-471E-8289-5A406F7C2C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A00C371-B2AF-BA40-95D1-CD6F5CD0271C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="19200" windowHeight="10100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="760" windowWidth="19200" windowHeight="10100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -363,7 +363,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -372,12 +372,10 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="7"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -410,7 +408,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Conversion Factors"/>
@@ -467,9 +465,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -507,9 +505,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -542,26 +540,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -594,26 +575,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -788,20 +752,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="12">
-        <v>44531</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C1" s="10">
+        <v>45296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -809,97 +773,97 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>2006</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B6" s="10" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B6" s="9" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>1.278</v>
       </c>
@@ -907,7 +871,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -923,33 +887,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.1796875" customWidth="1"/>
-    <col min="2" max="2" width="11.81640625" customWidth="1"/>
-    <col min="3" max="3" width="11.26953125" customWidth="1"/>
-    <col min="4" max="4" width="20.1796875" customWidth="1"/>
+    <col min="1" max="1" width="25.1640625" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -962,7 +926,7 @@
         <v>25879</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -975,7 +939,7 @@
         <v>25349</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -988,7 +952,7 @@
         <v>52050</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1001,7 +965,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1014,7 +978,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -1027,7 +991,7 @@
         <v>2574</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1040,7 +1004,7 @@
         <v>2688</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1053,7 +1017,7 @@
         <v>59869</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1066,7 +1030,7 @@
         <v>35138</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>31</v>
       </c>
@@ -1074,19 +1038,19 @@
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="14" t="s">
+      <c r="C14" s="11"/>
+      <c r="D14" s="12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1096,9 +1060,9 @@
       <c r="C15" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="14"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D15" s="12"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -1111,28 +1075,28 @@
         <v>3.5460000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>38</v>
       </c>
       <c r="B17">
         <v>95.55</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="6">
         <v>0</v>
       </c>
       <c r="D17" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>40</v>
       </c>
       <c r="B18">
         <v>44.67</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <f>C23*(B18/B23)</f>
         <v>13.041950354609931</v>
       </c>
@@ -1140,7 +1104,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1151,12 +1115,12 @@
         <v>58.48</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -1169,21 +1133,21 @@
         <v>1.671</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>38</v>
       </c>
       <c r="B22">
         <v>65.11</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="6">
         <v>0</v>
       </c>
       <c r="D22" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -1194,7 +1158,7 @@
         <v>14.82</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -1205,12 +1169,12 @@
         <v>58.48</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -1223,21 +1187,21 @@
         <v>1.6800000000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27">
         <v>65.11</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="6">
         <v>0</v>
       </c>
       <c r="D27" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1248,7 +1212,7 @@
         <v>14.82</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -1259,12 +1223,12 @@
         <v>58.48</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -1277,15 +1241,15 @@
         <v>3.7700000000000005</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="7">
         <f>AVERAGE(B27,B22,B17)</f>
         <v>75.256666666666661</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="6">
         <f>AVERAGE(C27,C22,C17)</f>
         <v>0</v>
       </c>
@@ -1293,15 +1257,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="7" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="6">
         <f t="shared" ref="B33:C34" si="0">AVERAGE(B28,B23,B18)</f>
         <v>48.73</v>
       </c>
-      <c r="C33" s="8">
+      <c r="C33" s="7">
         <f t="shared" si="0"/>
         <v>14.227316784869977</v>
       </c>
@@ -1309,15 +1273,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="7" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="6">
         <f t="shared" si="0"/>
         <v>58.48</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="6">
         <f t="shared" si="0"/>
         <v>58.48</v>
       </c>
@@ -1325,20 +1289,20 @@
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="7" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>46</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="9">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
         <f>(SUM(B16:B19)*B7+SUM(C16:C19)*C7+SUM(B21:B24)*B11+SUM(C21:C24)*C11+SUM(B26:B29)*B10+SUM(C26:C29)*C10+SUM(B31:B34)*B3+SUM(C31:C34)*C3)/SUM(B3:C3,B7:C7,B10:C11)</f>
         <v>120.76792682712498</v>
       </c>
@@ -1346,8 +1310,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="11">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="8">
         <f>A39*About!A27</f>
         <v>154.34141048506572</v>
       </c>
@@ -1370,17 +1334,17 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.1796875" customWidth="1"/>
+    <col min="1" max="1" width="31.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -1389,7 +1353,7 @@
         <v>154.34141048506572</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1398,15 +1362,15 @@
         <v>154.34141048506572</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1415,7 +1379,7 @@
         <v>154.34141048506572</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1423,7 +1387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
